--- a/dataFoodCPI/Benin_completes.xlsx
+++ b/dataFoodCPI/Benin_completes.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/harold/DataAnalyctisandScience/Cointegration_Johansen_test/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/harold/DataAnalyctisandScience/Cointegration_Johansen_test/dataFoodCPI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2EE3B5C-8941-FC4A-87D4-CD8C8878E8DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E80D1F45-9A24-B247-9F50-75F5E743330C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="34">
   <si>
     <t>Month</t>
   </si>
@@ -134,13 +134,16 @@
   <si>
     <t>Crude oil, WTI ($/bbl)</t>
   </si>
+  <si>
+    <t>Months</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -197,7 +200,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -510,7 +513,7 @@
   <sheetData>
     <row r="1" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
